--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38595" yWindow="1875" windowWidth="15330" windowHeight="10770" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PveCombatNpc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PveCombatNpc" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">PveCombatNpc!#REF!</definedName>
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -5326,18 +5326,38 @@
       <c r="AB53" s="23" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="n"/>
+      <c r="A54" s="21" t="n">
+        <v>90000017</v>
+      </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>赤焰妖狐</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="n"/>
-      <c r="E54" s="0" t="n"/>
-      <c r="G54" s="0" t="n"/>
-      <c r="H54" s="23" t="n"/>
-      <c r="I54" s="23" t="n"/>
-      <c r="J54" s="23" t="n"/>
+          <t>九幽守护者</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>9201,9202</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>boss_ai</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I54" s="23" t="n">
+        <v>55</v>
+      </c>
+      <c r="J54" s="23" t="n">
+        <v>200000</v>
+      </c>
       <c r="K54" s="23" t="n"/>
       <c r="L54" s="23" t="n"/>
       <c r="M54" s="23" t="n"/>
@@ -5356,6 +5376,38 @@
       <c r="Z54" s="23" t="n"/>
       <c r="AA54" s="23" t="n"/>
       <c r="AB54" s="23" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>赤焰妖狐</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="n"/>
+      <c r="E55" s="0" t="n"/>
+      <c r="G55" s="0" t="n"/>
+      <c r="H55" s="23" t="n"/>
+      <c r="I55" s="23" t="n"/>
+      <c r="J55" s="23" t="n"/>
+      <c r="K55" s="23" t="n"/>
+      <c r="L55" s="23" t="n"/>
+      <c r="M55" s="23" t="n"/>
+      <c r="N55" s="23" t="n"/>
+      <c r="O55" s="23" t="n"/>
+      <c r="P55" s="23" t="n"/>
+      <c r="Q55" s="23" t="n"/>
+      <c r="R55" s="23" t="n"/>
+      <c r="S55" s="23" t="n"/>
+      <c r="T55" s="23" t="n"/>
+      <c r="U55" s="23" t="n"/>
+      <c r="V55" s="23" t="n"/>
+      <c r="W55" s="23" t="n"/>
+      <c r="X55" s="23" t="n"/>
+      <c r="Y55" s="23" t="n"/>
+      <c r="Z55" s="23" t="n"/>
+      <c r="AA55" s="23" t="n"/>
+      <c r="AB55" s="23" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">

--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -4172,90 +4172,110 @@
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="8">
-      <c r="A37" s="21" t="n">
-        <v>25060001</v>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>魔龙 Razak</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>1099</v>
+      <c r="A37" s="18" t="n">
+        <v>90000001</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩1</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>1052</v>
       </c>
       <c r="D37" s="17" t="n"/>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>9001,9002,9003</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t>aggressive_ai</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I37" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K37" s="23" t="n"/>
-      <c r="L37" s="23" t="n"/>
-      <c r="M37" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="N37" s="23" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O37" s="23" t="n"/>
-      <c r="P37" s="23" t="n"/>
-      <c r="Q37" s="23" t="n"/>
-      <c r="R37" s="23" t="n"/>
-      <c r="S37" s="23" t="n"/>
-      <c r="T37" s="23" t="n"/>
-      <c r="U37" s="23" t="n"/>
-      <c r="V37" s="23" t="n"/>
-      <c r="W37" s="23" t="n"/>
-      <c r="X37" s="23" t="n"/>
-      <c r="Y37" s="23" t="n"/>
-      <c r="Z37" s="23" t="n"/>
-      <c r="AA37" s="23" t="n"/>
-      <c r="AB37" s="23" t="n"/>
+      <c r="H37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="13" t="n">
+        <v>1657</v>
+      </c>
+      <c r="S37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="13" t="n">
+        <v>1275</v>
+      </c>
       <c r="AC37" s="0" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="8">
       <c r="A38" s="18" t="n">
-        <v>90000001</v>
+        <v>90000002</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>测试木桩1</t>
+          <t>测试木桩2</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="H38" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0</v>
@@ -4273,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>1657</v>
+        <v>2932</v>
       </c>
       <c r="S38" s="13" t="n">
         <v>0</v>
@@ -4309,31 +4329,31 @@
     </row>
     <row r="39" ht="16.5" customHeight="1" s="8">
       <c r="A39" s="18" t="n">
-        <v>90000002</v>
+        <v>90000003</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>测试木桩2</t>
+          <t>测试木桩3</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D39" s="17" t="n"/>
       <c r="H39" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="K39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>0</v>
@@ -4351,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="R39" s="13" t="n">
-        <v>2932</v>
+        <v>1275</v>
       </c>
       <c r="S39" s="13" t="n">
         <v>0</v>
@@ -4387,111 +4407,111 @@
     </row>
     <row r="40" customFormat="1" s="23">
       <c r="A40" s="18" t="n">
-        <v>90000003</v>
+        <v>90000004</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>测试木桩3</t>
+          <t>测试木桩4</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D40" s="17" t="n"/>
       <c r="G40" s="23" t="n"/>
       <c r="H40" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="K40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="M40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="S40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB40" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="0" t="n"/>
     </row>
     <row r="41" customFormat="1" s="23">
       <c r="A41" s="18" t="n">
-        <v>90000004</v>
+        <v>90000005</v>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>测试木桩4</t>
+          <t>测试木桩5</t>
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D41" s="17" t="n"/>
       <c r="G41" s="23" t="n"/>
       <c r="H41" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="K41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="M41" s="13" t="n">
         <v>0</v>
@@ -4545,32 +4565,32 @@
     </row>
     <row r="42" customFormat="1" s="23">
       <c r="A42" s="18" t="n">
-        <v>90000005</v>
+        <v>90000006</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>测试木桩5</t>
+          <t>测试木桩6</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D42" s="17" t="n"/>
       <c r="G42" s="23" t="n"/>
       <c r="H42" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="K42" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="M42" s="13" t="n">
         <v>0</v>
@@ -4620,36 +4640,35 @@
       <c r="AB42" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" s="0" t="n"/>
     </row>
     <row r="43" customFormat="1" s="23">
       <c r="A43" s="18" t="n">
-        <v>90000006</v>
+        <v>90000007</v>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>测试木桩6</t>
+          <t>测试木桩7</t>
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D43" s="17" t="n"/>
       <c r="G43" s="23" t="n"/>
       <c r="H43" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="K43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="M43" s="13" t="n">
         <v>0</v>
@@ -4702,32 +4721,32 @@
     </row>
     <row r="44" customFormat="1" s="23">
       <c r="A44" s="18" t="n">
-        <v>90000007</v>
+        <v>90000008</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>测试木桩7</t>
+          <t>测试木桩8</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D44" s="17" t="n"/>
       <c r="G44" s="23" t="n"/>
       <c r="H44" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K44" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="M44" s="13" t="n">
         <v>0</v>
@@ -4780,32 +4799,32 @@
     </row>
     <row r="45" customFormat="1" s="23">
       <c r="A45" s="18" t="n">
-        <v>90000008</v>
+        <v>90000009</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>测试木桩8</t>
+          <t>测试木桩9</t>
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D45" s="17" t="n"/>
       <c r="G45" s="23" t="n"/>
       <c r="H45" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="K45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="M45" s="13" t="n">
         <v>0</v>
@@ -4858,32 +4877,32 @@
     </row>
     <row r="46" customFormat="1" s="23">
       <c r="A46" s="18" t="n">
-        <v>90000009</v>
+        <v>90000010</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>测试木桩9</t>
+          <t>测试木桩10</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D46" s="17" t="n"/>
       <c r="G46" s="23" t="n"/>
       <c r="H46" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="K46" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="M46" s="13" t="n">
         <v>0</v>
@@ -4936,32 +4955,32 @@
     </row>
     <row r="47" customFormat="1" s="23">
       <c r="A47" s="18" t="n">
-        <v>90000010</v>
+        <v>90000011</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>测试木桩10</t>
+          <t>测试木桩11</t>
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D47" s="17" t="n"/>
       <c r="G47" s="23" t="n"/>
       <c r="H47" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>100000000</v>
+        <v>500000000</v>
       </c>
       <c r="K47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>100000000</v>
+        <v>500000000</v>
       </c>
       <c r="M47" s="13" t="n">
         <v>0</v>
@@ -5014,32 +5033,31 @@
     </row>
     <row r="48" customFormat="1" s="23">
       <c r="A48" s="18" t="n">
-        <v>90000011</v>
+        <v>90000012</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>测试木桩11</t>
+          <t>测试木桩12</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D48" s="17" t="n"/>
-      <c r="G48" s="23" t="n"/>
-      <c r="H48" s="11" t="n">
-        <v>11</v>
+      <c r="H48" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="I48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="K48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="M48" s="13" t="n">
         <v>0</v>
@@ -5091,89 +5109,46 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
-        <v>90000012</v>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩12</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>1063</v>
-      </c>
-      <c r="D49" s="17" t="n"/>
-      <c r="H49" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="K49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="M49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="A49" s="21" t="n">
+        <v>90000013</v>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>擂台挑战者</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="H49" s="23" t="n"/>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="23" t="n"/>
+      <c r="K49" s="23" t="n"/>
+      <c r="L49" s="23" t="n"/>
+      <c r="M49" s="23" t="n"/>
+      <c r="N49" s="23" t="n"/>
+      <c r="O49" s="23" t="n"/>
+      <c r="P49" s="23" t="n"/>
+      <c r="Q49" s="23" t="n"/>
+      <c r="R49" s="23" t="n"/>
+      <c r="S49" s="23" t="n"/>
+      <c r="T49" s="23" t="n"/>
+      <c r="U49" s="23" t="n"/>
+      <c r="V49" s="23" t="n"/>
+      <c r="W49" s="23" t="n"/>
+      <c r="X49" s="23" t="n"/>
+      <c r="Y49" s="23" t="n"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="23" t="n"/>
+      <c r="AB49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="21" t="n">
-        <v>90000013</v>
+        <v>90000014</v>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>擂台挑战者</t>
+          <t>剑修挑战者</t>
         </is>
       </c>
       <c r="C50" s="24" t="n">
@@ -5203,15 +5178,15 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="n">
+        <v>90000015</v>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>剑修挑战者</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="n">
         <v>90000014</v>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>剑修挑战者</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="n">
-        <v>1012</v>
       </c>
       <c r="H51" s="23" t="n"/>
       <c r="I51" s="23" t="n"/>
@@ -5236,17 +5211,13 @@
       <c r="AB51" s="23" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="n">
-        <v>90000015</v>
-      </c>
+      <c r="A52" s="21" t="n"/>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>剑修挑战者</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="n">
-        <v>90000014</v>
-      </c>
+          <t>赤焰妖狐</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="n"/>
       <c r="H52" s="23" t="n"/>
       <c r="I52" s="23" t="n"/>
       <c r="J52" s="23" t="n"/>
@@ -5268,146 +5239,6 @@
       <c r="Z52" s="23" t="n"/>
       <c r="AA52" s="23" t="n"/>
       <c r="AB52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="n">
-        <v>90000016</v>
-      </c>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>魔龙 Razak</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="n">
-        <v>1099</v>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
-        <is>
-          <t>[9001,9002,9003]</t>
-        </is>
-      </c>
-      <c r="G53" s="0" t="inlineStr">
-        <is>
-          <t>aggressive_ai</t>
-        </is>
-      </c>
-      <c r="H53" s="23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I53" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="J53" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K53" s="23" t="n"/>
-      <c r="L53" s="23" t="n"/>
-      <c r="M53" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="N53" s="23" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O53" s="23" t="n"/>
-      <c r="P53" s="23" t="n"/>
-      <c r="Q53" s="23" t="n"/>
-      <c r="R53" s="23" t="n"/>
-      <c r="S53" s="23" t="n"/>
-      <c r="T53" s="23" t="n"/>
-      <c r="U53" s="23" t="n"/>
-      <c r="V53" s="23" t="n"/>
-      <c r="W53" s="23" t="n"/>
-      <c r="X53" s="23" t="n"/>
-      <c r="Y53" s="23" t="n"/>
-      <c r="Z53" s="23" t="n"/>
-      <c r="AA53" s="23" t="n"/>
-      <c r="AB53" s="23" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="21" t="n">
-        <v>90000017</v>
-      </c>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>九幽守护者</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="n">
-        <v>1150</v>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
-        <is>
-          <t>9201,9202</t>
-        </is>
-      </c>
-      <c r="G54" s="0" t="inlineStr">
-        <is>
-          <t>boss_ai</t>
-        </is>
-      </c>
-      <c r="H54" s="23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I54" s="23" t="n">
-        <v>55</v>
-      </c>
-      <c r="J54" s="23" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K54" s="23" t="n"/>
-      <c r="L54" s="23" t="n"/>
-      <c r="M54" s="23" t="n"/>
-      <c r="N54" s="23" t="n"/>
-      <c r="O54" s="23" t="n"/>
-      <c r="P54" s="23" t="n"/>
-      <c r="Q54" s="23" t="n"/>
-      <c r="R54" s="23" t="n"/>
-      <c r="S54" s="23" t="n"/>
-      <c r="T54" s="23" t="n"/>
-      <c r="U54" s="23" t="n"/>
-      <c r="V54" s="23" t="n"/>
-      <c r="W54" s="23" t="n"/>
-      <c r="X54" s="23" t="n"/>
-      <c r="Y54" s="23" t="n"/>
-      <c r="Z54" s="23" t="n"/>
-      <c r="AA54" s="23" t="n"/>
-      <c r="AB54" s="23" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="n"/>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>赤焰妖狐</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="n"/>
-      <c r="E55" s="0" t="n"/>
-      <c r="G55" s="0" t="n"/>
-      <c r="H55" s="23" t="n"/>
-      <c r="I55" s="23" t="n"/>
-      <c r="J55" s="23" t="n"/>
-      <c r="K55" s="23" t="n"/>
-      <c r="L55" s="23" t="n"/>
-      <c r="M55" s="23" t="n"/>
-      <c r="N55" s="23" t="n"/>
-      <c r="O55" s="23" t="n"/>
-      <c r="P55" s="23" t="n"/>
-      <c r="Q55" s="23" t="n"/>
-      <c r="R55" s="23" t="n"/>
-      <c r="S55" s="23" t="n"/>
-      <c r="T55" s="23" t="n"/>
-      <c r="U55" s="23" t="n"/>
-      <c r="V55" s="23" t="n"/>
-      <c r="W55" s="23" t="n"/>
-      <c r="X55" s="23" t="n"/>
-      <c r="Y55" s="23" t="n"/>
-      <c r="Z55" s="23" t="n"/>
-      <c r="AA55" s="23" t="n"/>
-      <c r="AB55" s="23" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">

--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38595" yWindow="1875" windowWidth="15330" windowHeight="10770" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PveCombatNpc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PveCombatNpc" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">PveCombatNpc!#REF!</definedName>
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -5211,20 +5211,39 @@
       <c r="AB51" s="23" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="n"/>
+      <c r="A52" s="21" t="n">
+        <v>90000016</v>
+      </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>赤焰妖狐</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="n"/>
-      <c r="H52" s="23" t="n"/>
-      <c r="I52" s="23" t="n"/>
-      <c r="J52" s="23" t="n"/>
+          <t>冰封君主</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>9001,9002,9003</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="J52" s="23" t="n">
+        <v>800000</v>
+      </c>
       <c r="K52" s="23" t="n"/>
       <c r="L52" s="23" t="n"/>
-      <c r="M52" s="23" t="n"/>
-      <c r="N52" s="23" t="n"/>
+      <c r="M52" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N52" s="23" t="n">
+        <v>40000</v>
+      </c>
       <c r="O52" s="23" t="n"/>
       <c r="P52" s="23" t="n"/>
       <c r="Q52" s="23" t="n"/>
@@ -5239,6 +5258,37 @@
       <c r="Z52" s="23" t="n"/>
       <c r="AA52" s="23" t="n"/>
       <c r="AB52" s="23" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>赤焰妖狐</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="n"/>
+      <c r="E53" s="0" t="n"/>
+      <c r="H53" s="23" t="n"/>
+      <c r="I53" s="23" t="n"/>
+      <c r="J53" s="23" t="n"/>
+      <c r="K53" s="23" t="n"/>
+      <c r="L53" s="23" t="n"/>
+      <c r="M53" s="23" t="n"/>
+      <c r="N53" s="23" t="n"/>
+      <c r="O53" s="23" t="n"/>
+      <c r="P53" s="23" t="n"/>
+      <c r="Q53" s="23" t="n"/>
+      <c r="R53" s="23" t="n"/>
+      <c r="S53" s="23" t="n"/>
+      <c r="T53" s="23" t="n"/>
+      <c r="U53" s="23" t="n"/>
+      <c r="V53" s="23" t="n"/>
+      <c r="W53" s="23" t="n"/>
+      <c r="X53" s="23" t="n"/>
+      <c r="Y53" s="23" t="n"/>
+      <c r="Z53" s="23" t="n"/>
+      <c r="AA53" s="23" t="n"/>
+      <c r="AB53" s="23" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">

--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -398,7 +398,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -468,15 +468,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1315,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1718,7 +1709,7 @@
         <v>1012</v>
       </c>
       <c r="D5" s="17" t="n"/>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1806,7 +1797,7 @@
         <v>1012</v>
       </c>
       <c r="D6" s="17" t="n"/>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1895,7 +1886,7 @@
         <v>1057</v>
       </c>
       <c r="D7" s="17" t="n"/>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1983,7 +1974,7 @@
         <v>1060</v>
       </c>
       <c r="D8" s="17" t="n"/>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2071,7 +2062,7 @@
         <v>1062</v>
       </c>
       <c r="D9" s="17" t="n"/>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2159,7 +2150,7 @@
         <v>1012</v>
       </c>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2257,7 +2248,7 @@
       <c r="A12" s="18" t="n">
         <v>8032</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>分身</t>
         </is>
@@ -2296,7 +2287,7 @@
       <c r="I13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J13" s="16" t="n">
         <v>2000</v>
       </c>
       <c r="K13" s="13" t="n">
@@ -3434,1861 +3425,1665 @@
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="8">
-      <c r="A28" s="21" t="n">
-        <v>1065601</v>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>杨戬</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>1065</v>
-      </c>
-      <c r="D28" s="23" t="n">
+      <c r="A28" s="18" t="n">
+        <v>90000001</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩1</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D28" s="17" t="n"/>
+      <c r="H28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="23" t="n">
-        <v>10010001</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="J28" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M28" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N28" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q28" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V28" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="W28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB28" s="23" t="n">
-        <v>100</v>
+      <c r="I28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13" t="n">
+        <v>1657</v>
+      </c>
+      <c r="S28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC28" s="0" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="8">
-      <c r="A29" s="21" t="n">
-        <v>1065602</v>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>李靖</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D29" s="23" t="n">
+      <c r="A29" s="18" t="n">
+        <v>90000002</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩2</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D29" s="17" t="n"/>
+      <c r="H29" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="23" t="n">
-        <v>10010002</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I29" s="23" t="n">
-        <v>450</v>
-      </c>
-      <c r="J29" s="23" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M29" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N29" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O29" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="P29" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q29" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="R29" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S29" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="T29" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U29" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V29" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB29" s="23" t="n">
-        <v>100</v>
+      <c r="I29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>2932</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC29" s="0" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="8">
-      <c r="A30" s="21" t="n">
-        <v>1065603</v>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>哪吒</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D30" s="23" t="n">
+      <c r="A30" s="18" t="n">
+        <v>90000003</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩3</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D30" s="17" t="n"/>
+      <c r="H30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="23" t="n">
-        <v>10010003</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J30" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O30" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P30" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q30" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S30" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U30" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="W30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB30" s="23" t="n">
-        <v>100</v>
+      <c r="I30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC30" s="0" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="8">
-      <c r="A31" s="21" t="n">
-        <v>1065604</v>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>梅山·康太尉</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>1058</v>
-      </c>
-      <c r="D31" s="23" t="n">
+      <c r="A31" s="18" t="n">
+        <v>90000004</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩4</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D31" s="17" t="n"/>
+      <c r="H31" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="23" t="n">
-        <v>10010004</v>
-      </c>
-      <c r="H31" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I31" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J31" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L31" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N31" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P31" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q31" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R31" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="W31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB31" s="23" t="n">
-        <v>100</v>
+      <c r="I31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="AC31" s="0" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="8">
-      <c r="A32" s="21" t="n">
-        <v>1065605</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>梅山·张太尉</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D32" s="23" t="n">
+      <c r="A32" s="18" t="n">
+        <v>90000005</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩5</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D32" s="17" t="n"/>
+      <c r="H32" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="23" t="n">
-        <v>10010005</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J32" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L32" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N32" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P32" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q32" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T32" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U32" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="V32" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB32" s="23" t="n">
-        <v>100</v>
+      <c r="I32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="AC32" s="0" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="8">
-      <c r="A33" s="21" t="n">
-        <v>1065606</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>梅山·李太尉</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D33" s="23" t="n">
+      <c r="A33" s="18" t="n">
+        <v>90000006</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩6</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D33" s="17" t="n"/>
+      <c r="H33" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G33" s="23" t="n">
-        <v>10010006</v>
-      </c>
-      <c r="H33" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J33" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L33" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M33" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="N33" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O33" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q33" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S33" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T33" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U33" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB33" s="23" t="n">
-        <v>100</v>
+      <c r="I33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="8">
-      <c r="A34" s="21" t="n">
-        <v>1065607</v>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>梅山·姚太尉</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D34" s="23" t="n">
+      <c r="A34" s="18" t="n">
+        <v>90000007</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩7</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D34" s="17" t="n"/>
+      <c r="H34" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G34" s="23" t="n">
-        <v>10010007</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J34" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L34" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N34" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O34" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P34" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q34" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="R34" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S34" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T34" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V34" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB34" s="23" t="n">
-        <v>100</v>
+      <c r="I34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="8">
-      <c r="A35" s="21" t="n">
-        <v>1065609</v>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>巨灵神</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="A35" s="18" t="n">
+        <v>90000008</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩8</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
         <v>1059</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="17" t="n"/>
+      <c r="H35" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G35" s="23" t="n">
-        <v>10010008</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J35" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L35" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M35" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="N35" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O35" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P35" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q35" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R35" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S35" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U35" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V35" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB35" s="23" t="n">
-        <v>100</v>
+      <c r="I35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="8">
-      <c r="A36" s="21" t="n">
-        <v>1065611</v>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>哮天犬</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>1052</v>
+      <c r="A36" s="18" t="n">
+        <v>90000009</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩9</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>1060</v>
       </c>
       <c r="D36" s="17" t="n"/>
-      <c r="H36" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="J36" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L36" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M36" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="N36" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O36" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q36" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R36" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S36" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U36" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V36" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB36" s="23" t="n">
-        <v>100</v>
+      <c r="H36" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="8">
       <c r="A37" s="18" t="n">
-        <v>90000001</v>
+        <v>90000010</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>测试木桩1</t>
+          <t>测试木桩10</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="D37" s="17" t="n"/>
       <c r="H37" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>10</v>
+        <v>100000000</v>
       </c>
       <c r="K37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>10</v>
+        <v>100000000</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="13" t="n">
-        <v>1657</v>
+        <v>0</v>
       </c>
       <c r="S37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB37" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC37" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="8">
       <c r="A38" s="18" t="n">
-        <v>90000002</v>
+        <v>90000011</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>测试木桩2</t>
+          <t>测试木桩11</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1053</v>
+        <v>1062</v>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="H38" s="11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>100</v>
+        <v>500000000</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>100</v>
+        <v>500000000</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>2932</v>
+        <v>0</v>
       </c>
       <c r="S38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB38" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC38" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="8">
       <c r="A39" s="18" t="n">
-        <v>90000003</v>
+        <v>90000012</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>测试木桩3</t>
+          <t>测试木桩12</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="D39" s="17" t="n"/>
-      <c r="H39" s="11" t="n">
-        <v>3</v>
+      <c r="H39" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="K39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="S39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB39" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC39" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="1" s="23">
-      <c r="A40" s="18" t="n">
-        <v>90000004</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩4</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D40" s="17" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="0" t="n"/>
+      <c r="A40" s="21" t="n">
+        <v>1065601</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>杨戬</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>10010001</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="J40" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M40" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N40" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P40" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q40" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V40" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="W40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB40" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41" customFormat="1" s="23">
-      <c r="A41" s="18" t="n">
-        <v>90000005</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩5</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D41" s="17" t="n"/>
-      <c r="G41" s="23" t="n"/>
-      <c r="H41" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="0" t="n"/>
+      <c r="A41" s="21" t="n">
+        <v>1065602</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>李靖</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>10010002</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="J41" s="23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L41" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M41" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N41" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O41" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P41" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q41" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S41" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T41" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U41" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V41" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB41" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="42" customFormat="1" s="23">
-      <c r="A42" s="18" t="n">
-        <v>90000006</v>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩6</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="13" t="n">
-        <v>0</v>
+      <c r="A42" s="21" t="n">
+        <v>1065603</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>哪吒</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>10010003</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J42" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O42" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P42" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q42" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="R42" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S42" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="W42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="43" customFormat="1" s="23">
-      <c r="A43" s="18" t="n">
-        <v>90000007</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩7</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="n">
+      <c r="A43" s="21" t="n">
+        <v>1065604</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>梅山·康太尉</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
         <v>1058</v>
       </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="M43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="13" t="n">
-        <v>0</v>
+      <c r="D43" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>10010004</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J43" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L43" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q43" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V43" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="W43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB43" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="1" s="23">
-      <c r="A44" s="18" t="n">
-        <v>90000008</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩8</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>1059</v>
-      </c>
-      <c r="D44" s="17" t="n"/>
-      <c r="G44" s="23" t="n"/>
-      <c r="H44" s="11" t="n">
+      <c r="A44" s="21" t="n">
+        <v>1065605</v>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>梅山·张太尉</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>10010005</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L44" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O44" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="13" t="n">
-        <v>0</v>
+      <c r="P44" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S44" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U44" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="V44" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB44" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="45" customFormat="1" s="23">
-      <c r="A45" s="18" t="n">
-        <v>90000009</v>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩9</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D45" s="17" t="n"/>
-      <c r="G45" s="23" t="n"/>
-      <c r="H45" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="13" t="n">
-        <v>0</v>
+      <c r="A45" s="21" t="n">
+        <v>1065606</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>梅山·李太尉</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>10010006</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J45" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M45" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N45" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O45" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S45" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U45" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V45" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB45" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="46" customFormat="1" s="23">
-      <c r="A46" s="18" t="n">
-        <v>90000010</v>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩10</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D46" s="17" t="n"/>
-      <c r="G46" s="23" t="n"/>
-      <c r="H46" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="13" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="13" t="n">
-        <v>0</v>
+      <c r="A46" s="21" t="n">
+        <v>1065607</v>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>梅山·姚太尉</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>10010007</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J46" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L46" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O46" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P46" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q46" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="R46" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S46" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB46" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="1" s="23">
-      <c r="A47" s="18" t="n">
-        <v>90000011</v>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩11</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>1062</v>
-      </c>
-      <c r="D47" s="17" t="n"/>
-      <c r="G47" s="23" t="n"/>
-      <c r="H47" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="K47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="13" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="M47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="13" t="n">
-        <v>0</v>
+      <c r="A47" s="21" t="n">
+        <v>1065609</v>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>巨灵神</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>10010008</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J47" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M47" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="N47" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O47" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U47" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V47" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB47" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="1" s="23">
-      <c r="A48" s="18" t="n">
-        <v>90000012</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩12</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>1063</v>
-      </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="H48" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="M48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="n">
-        <v>90000013</v>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>擂台挑战者</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="n">
-        <v>1012</v>
-      </c>
-      <c r="H49" s="23" t="n"/>
-      <c r="I49" s="23" t="n"/>
-      <c r="J49" s="23" t="n"/>
-      <c r="K49" s="23" t="n"/>
-      <c r="L49" s="23" t="n"/>
-      <c r="M49" s="23" t="n"/>
-      <c r="N49" s="23" t="n"/>
-      <c r="O49" s="23" t="n"/>
-      <c r="P49" s="23" t="n"/>
-      <c r="Q49" s="23" t="n"/>
-      <c r="R49" s="23" t="n"/>
-      <c r="S49" s="23" t="n"/>
-      <c r="T49" s="23" t="n"/>
-      <c r="U49" s="23" t="n"/>
-      <c r="V49" s="23" t="n"/>
-      <c r="W49" s="23" t="n"/>
-      <c r="X49" s="23" t="n"/>
-      <c r="Y49" s="23" t="n"/>
-      <c r="Z49" s="23" t="n"/>
-      <c r="AA49" s="23" t="n"/>
-      <c r="AB49" s="23" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="n">
-        <v>90000014</v>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>剑修挑战者</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="n">
-        <v>1012</v>
-      </c>
-      <c r="H50" s="23" t="n"/>
-      <c r="I50" s="23" t="n"/>
-      <c r="J50" s="23" t="n"/>
-      <c r="K50" s="23" t="n"/>
-      <c r="L50" s="23" t="n"/>
-      <c r="M50" s="23" t="n"/>
-      <c r="N50" s="23" t="n"/>
-      <c r="O50" s="23" t="n"/>
-      <c r="P50" s="23" t="n"/>
-      <c r="Q50" s="23" t="n"/>
-      <c r="R50" s="23" t="n"/>
-      <c r="S50" s="23" t="n"/>
-      <c r="T50" s="23" t="n"/>
-      <c r="U50" s="23" t="n"/>
-      <c r="V50" s="23" t="n"/>
-      <c r="W50" s="23" t="n"/>
-      <c r="X50" s="23" t="n"/>
-      <c r="Y50" s="23" t="n"/>
-      <c r="Z50" s="23" t="n"/>
-      <c r="AA50" s="23" t="n"/>
-      <c r="AB50" s="23" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="21" t="n">
-        <v>90000015</v>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>剑修挑战者</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="n">
-        <v>90000014</v>
-      </c>
-      <c r="H51" s="23" t="n"/>
-      <c r="I51" s="23" t="n"/>
-      <c r="J51" s="23" t="n"/>
-      <c r="K51" s="23" t="n"/>
-      <c r="L51" s="23" t="n"/>
-      <c r="M51" s="23" t="n"/>
-      <c r="N51" s="23" t="n"/>
-      <c r="O51" s="23" t="n"/>
-      <c r="P51" s="23" t="n"/>
-      <c r="Q51" s="23" t="n"/>
-      <c r="R51" s="23" t="n"/>
-      <c r="S51" s="23" t="n"/>
-      <c r="T51" s="23" t="n"/>
-      <c r="U51" s="23" t="n"/>
-      <c r="V51" s="23" t="n"/>
-      <c r="W51" s="23" t="n"/>
-      <c r="X51" s="23" t="n"/>
-      <c r="Y51" s="23" t="n"/>
-      <c r="Z51" s="23" t="n"/>
-      <c r="AA51" s="23" t="n"/>
-      <c r="AB51" s="23" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="n">
-        <v>90000016</v>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>冰封君主</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="n">
-        <v>1300</v>
-      </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t>9001,9002,9003</t>
-        </is>
-      </c>
-      <c r="H52" s="23" t="n">
-        <v>90</v>
-      </c>
-      <c r="I52" s="23" t="n">
+      <c r="A48" s="21" t="n">
+        <v>1065611</v>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>哮天犬</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H48" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="J52" s="23" t="n">
-        <v>800000</v>
-      </c>
-      <c r="K52" s="23" t="n"/>
-      <c r="L52" s="23" t="n"/>
-      <c r="M52" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="N52" s="23" t="n">
-        <v>40000</v>
-      </c>
-      <c r="O52" s="23" t="n"/>
-      <c r="P52" s="23" t="n"/>
-      <c r="Q52" s="23" t="n"/>
-      <c r="R52" s="23" t="n"/>
-      <c r="S52" s="23" t="n"/>
-      <c r="T52" s="23" t="n"/>
-      <c r="U52" s="23" t="n"/>
-      <c r="V52" s="23" t="n"/>
-      <c r="W52" s="23" t="n"/>
-      <c r="X52" s="23" t="n"/>
-      <c r="Y52" s="23" t="n"/>
-      <c r="Z52" s="23" t="n"/>
-      <c r="AA52" s="23" t="n"/>
-      <c r="AB52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="n"/>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>赤焰妖狐</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="n"/>
-      <c r="E53" s="0" t="n"/>
-      <c r="H53" s="23" t="n"/>
-      <c r="I53" s="23" t="n"/>
-      <c r="J53" s="23" t="n"/>
-      <c r="K53" s="23" t="n"/>
-      <c r="L53" s="23" t="n"/>
-      <c r="M53" s="23" t="n"/>
-      <c r="N53" s="23" t="n"/>
-      <c r="O53" s="23" t="n"/>
-      <c r="P53" s="23" t="n"/>
-      <c r="Q53" s="23" t="n"/>
-      <c r="R53" s="23" t="n"/>
-      <c r="S53" s="23" t="n"/>
-      <c r="T53" s="23" t="n"/>
-      <c r="U53" s="23" t="n"/>
-      <c r="V53" s="23" t="n"/>
-      <c r="W53" s="23" t="n"/>
-      <c r="X53" s="23" t="n"/>
-      <c r="Y53" s="23" t="n"/>
-      <c r="Z53" s="23" t="n"/>
-      <c r="AA53" s="23" t="n"/>
-      <c r="AB53" s="23" t="n"/>
+      <c r="I48" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="J48" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L48" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M48" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="N48" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q48" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U48" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="V48" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB48" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">

--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -398,7 +398,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -468,6 +468,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1306,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1709,7 +1718,7 @@
         <v>1012</v>
       </c>
       <c r="D5" s="17" t="n"/>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1797,7 +1806,7 @@
         <v>1012</v>
       </c>
       <c r="D6" s="17" t="n"/>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1886,7 +1895,7 @@
         <v>1057</v>
       </c>
       <c r="D7" s="17" t="n"/>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1974,7 +1983,7 @@
         <v>1060</v>
       </c>
       <c r="D8" s="17" t="n"/>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2062,7 +2071,7 @@
         <v>1062</v>
       </c>
       <c r="D9" s="17" t="n"/>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2150,7 +2159,7 @@
         <v>1012</v>
       </c>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2248,7 +2257,7 @@
       <c r="A12" s="18" t="n">
         <v>8032</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>分身</t>
         </is>
@@ -2287,7 +2296,7 @@
       <c r="I13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="27" t="n">
         <v>2000</v>
       </c>
       <c r="K13" s="13" t="n">
@@ -3425,1665 +3434,1720 @@
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="8">
-      <c r="A28" s="18" t="n">
-        <v>90000001</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩1</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
+      <c r="A28" s="21" t="n">
+        <v>1065601</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>杨戬</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>10010001</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M28" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N28" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q28" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R28" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V28" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="W28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA28" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC28" s="0" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="8">
+      <c r="A29" s="21" t="n">
+        <v>1065602</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>李靖</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>10010002</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I29" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K29" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M29" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N29" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O29" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q29" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="R29" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S29" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U29" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V29" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W29" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X29" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y29" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA29" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC29" s="0" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="8">
+      <c r="A30" s="21" t="n">
+        <v>1065603</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>哪吒</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>10010003</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K30" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M30" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O30" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q30" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="R30" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S30" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U30" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="W30" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X30" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y30" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z30" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA30" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB30" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC30" s="0" t="n"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="8">
+      <c r="A31" s="21" t="n">
+        <v>1065604</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>梅山·康太尉</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>10010004</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K31" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M31" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O31" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P31" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q31" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R31" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S31" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U31" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="W31" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X31" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y31" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA31" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB31" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC31" s="0" t="n"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="8">
+      <c r="A32" s="21" t="n">
+        <v>1065605</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>梅山·张太尉</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>10010005</v>
+      </c>
+      <c r="H32" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I32" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J32" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K32" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L32" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M32" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O32" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P32" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q32" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S32" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U32" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="V32" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W32" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X32" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB32" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="0" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="8">
+      <c r="A33" s="21" t="n">
+        <v>1065606</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>梅山·李太尉</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>10010006</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I33" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J33" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M33" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N33" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O33" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q33" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S33" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U33" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W33" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X33" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y33" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA33" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB33" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="8">
+      <c r="A34" s="21" t="n">
+        <v>1065607</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>梅山·姚太尉</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>10010007</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J34" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L34" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O34" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P34" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q34" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="R34" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S34" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T34" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V34" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X34" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z34" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB34" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="8">
+      <c r="A35" s="21" t="n">
+        <v>1065609</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>巨灵神</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="23" t="n">
+        <v>10010008</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J35" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L35" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M35" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="N35" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O35" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S35" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U35" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V35" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W35" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X35" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z35" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA35" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB35" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="8">
+      <c r="A36" s="21" t="n">
+        <v>1065611</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>哮天犬</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="n">
         <v>1052</v>
       </c>
-      <c r="D28" s="17" t="n"/>
-      <c r="H28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13" t="n">
-        <v>3187</v>
-      </c>
-      <c r="O28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13" t="n">
-        <v>2550</v>
-      </c>
-      <c r="Q28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13" t="n">
-        <v>1657</v>
-      </c>
-      <c r="S28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="U28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="W28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="Y28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AA28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC28" s="0" t="n"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" s="8">
-      <c r="A29" s="18" t="n">
-        <v>90000002</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩2</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="n">
-        <v>1053</v>
-      </c>
-      <c r="D29" s="17" t="n"/>
-      <c r="H29" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>3187</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13" t="n">
-        <v>2550</v>
-      </c>
-      <c r="Q29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13" t="n">
-        <v>2932</v>
-      </c>
-      <c r="S29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="U29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="W29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="Y29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AA29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC29" s="0" t="n"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="8">
-      <c r="A30" s="18" t="n">
-        <v>90000003</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩3</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>1054</v>
-      </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="H30" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="13" t="n">
+      <c r="D36" s="17" t="n"/>
+      <c r="H36" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="J36" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="K30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="13" t="n">
-        <v>3187</v>
-      </c>
-      <c r="O30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13" t="n">
-        <v>2550</v>
-      </c>
-      <c r="Q30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="S30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="U30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="W30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="Y30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AA30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC30" s="0" t="n"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" s="8">
-      <c r="A31" s="18" t="n">
-        <v>90000004</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩4</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D31" s="17" t="n"/>
-      <c r="H31" s="11" t="n">
+      <c r="K36" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M36" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="N36" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O36" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="0" t="n"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="8">
-      <c r="A32" s="18" t="n">
-        <v>90000005</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩5</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D32" s="17" t="n"/>
-      <c r="H32" s="11" t="n">
+      <c r="P36" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q36" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="0" t="n"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" s="8">
-      <c r="A33" s="18" t="n">
-        <v>90000006</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩6</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D33" s="17" t="n"/>
-      <c r="H33" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="8">
-      <c r="A34" s="18" t="n">
-        <v>90000007</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩7</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>1058</v>
-      </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="H34" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="M34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="8">
-      <c r="A35" s="18" t="n">
-        <v>90000008</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩8</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>1059</v>
-      </c>
-      <c r="D35" s="17" t="n"/>
-      <c r="H35" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="M35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="8">
-      <c r="A36" s="18" t="n">
-        <v>90000009</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩9</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="H36" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="K36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="M36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="13" t="n">
-        <v>0</v>
+      <c r="R36" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S36" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U36" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="V36" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W36" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X36" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y36" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA36" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB36" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="8">
       <c r="A37" s="18" t="n">
-        <v>90000010</v>
+        <v>90000001</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>测试木桩10</t>
+          <t>测试木桩1</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="D37" s="17" t="n"/>
       <c r="H37" s="11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>100000000</v>
+        <v>10</v>
       </c>
       <c r="K37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>100000000</v>
+        <v>10</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>0</v>
+        <v>3187</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="Q37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="13" t="n">
-        <v>0</v>
+        <v>1657</v>
       </c>
       <c r="S37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="U37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="W37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="Y37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="AA37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB37" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="AC37" s="0" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="8">
       <c r="A38" s="18" t="n">
-        <v>90000011</v>
+        <v>90000002</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>测试木桩11</t>
+          <t>测试木桩2</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="H38" s="11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>500000000</v>
+        <v>100</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>500000000</v>
+        <v>100</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>0</v>
+        <v>3187</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="Q38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>0</v>
+        <v>2932</v>
       </c>
       <c r="S38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="U38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="W38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="Y38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z38" s="13" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="AA38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB38" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="AC38" s="0" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="8">
       <c r="A39" s="18" t="n">
+        <v>90000003</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩3</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D39" s="17" t="n"/>
+      <c r="H39" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AC39" s="0" t="n"/>
+    </row>
+    <row r="40" customFormat="1" s="23">
+      <c r="A40" s="18" t="n">
+        <v>90000004</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩4</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D40" s="17" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="0" t="n"/>
+    </row>
+    <row r="41" customFormat="1" s="23">
+      <c r="A41" s="18" t="n">
+        <v>90000005</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩5</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D41" s="17" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="0" t="n"/>
+    </row>
+    <row r="42" customFormat="1" s="23">
+      <c r="A42" s="18" t="n">
+        <v>90000006</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩6</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D42" s="17" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" s="23">
+      <c r="A43" s="18" t="n">
+        <v>90000007</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩7</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D43" s="17" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" s="23">
+      <c r="A44" s="18" t="n">
+        <v>90000008</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩8</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D44" s="17" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" s="23">
+      <c r="A45" s="18" t="n">
+        <v>90000009</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩9</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D45" s="17" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" s="23">
+      <c r="A46" s="18" t="n">
+        <v>90000010</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩10</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D46" s="17" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" s="23">
+      <c r="A47" s="18" t="n">
+        <v>90000011</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩11</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D47" s="17" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" s="23">
+      <c r="A48" s="18" t="n">
         <v>90000012</v>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>测试木桩12</t>
         </is>
       </c>
-      <c r="C39" s="17" t="n">
+      <c r="C48" s="17" t="n">
         <v>1063</v>
       </c>
-      <c r="D39" s="17" t="n"/>
-      <c r="H39" s="13" t="n">
+      <c r="D48" s="17" t="n"/>
+      <c r="H48" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="13" t="n">
+      <c r="I48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13" t="n">
         <v>1000000000</v>
       </c>
-      <c r="K39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="13" t="n">
+      <c r="K48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="13" t="n">
         <v>1000000000</v>
       </c>
-      <c r="M39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" s="23">
-      <c r="A40" s="21" t="n">
-        <v>1065601</v>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>杨戬</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="n">
-        <v>1065</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>10010001</v>
-      </c>
-      <c r="H40" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="J40" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L40" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M40" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N40" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P40" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q40" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V40" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="W40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z40" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA40" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB40" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" s="23">
-      <c r="A41" s="21" t="n">
-        <v>1065602</v>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>李靖</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D41" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>10010002</v>
-      </c>
-      <c r="H41" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>450</v>
-      </c>
-      <c r="J41" s="23" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K41" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L41" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M41" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N41" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O41" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="P41" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q41" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S41" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="T41" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U41" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V41" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W41" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X41" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y41" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z41" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA41" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB41" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" s="23">
-      <c r="A42" s="21" t="n">
-        <v>1065603</v>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>哪吒</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="23" t="n">
-        <v>10010003</v>
-      </c>
-      <c r="H42" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J42" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L42" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M42" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N42" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O42" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P42" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q42" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="R42" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S42" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T42" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U42" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V42" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="W42" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X42" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y42" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z42" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA42" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB42" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" s="23">
-      <c r="A43" s="21" t="n">
-        <v>1065604</v>
-      </c>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>梅山·康太尉</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>1058</v>
-      </c>
-      <c r="D43" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" s="23" t="n">
-        <v>10010004</v>
-      </c>
-      <c r="H43" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I43" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J43" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L43" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M43" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N43" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O43" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P43" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q43" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S43" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T43" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U43" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="V43" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="W43" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X43" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y43" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z43" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA43" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB43" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" s="23">
-      <c r="A44" s="21" t="n">
-        <v>1065605</v>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>梅山·张太尉</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D44" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" s="23" t="n">
-        <v>10010005</v>
-      </c>
-      <c r="H44" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J44" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L44" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M44" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N44" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O44" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P44" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q44" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R44" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S44" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T44" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U44" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="V44" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W44" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X44" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y44" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z44" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA44" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB44" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" s="23">
-      <c r="A45" s="21" t="n">
-        <v>1065606</v>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>梅山·李太尉</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>10010006</v>
-      </c>
-      <c r="H45" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J45" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K45" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L45" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M45" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="N45" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O45" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P45" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q45" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R45" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S45" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T45" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U45" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="V45" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W45" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X45" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y45" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA45" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB45" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" s="23">
-      <c r="A46" s="21" t="n">
-        <v>1065607</v>
-      </c>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>梅山·姚太尉</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>10010007</v>
-      </c>
-      <c r="H46" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I46" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J46" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K46" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L46" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N46" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O46" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P46" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q46" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="R46" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S46" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T46" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V46" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X46" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z46" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB46" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" s="23">
-      <c r="A47" s="21" t="n">
-        <v>1065609</v>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>巨灵神</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="n">
-        <v>1059</v>
-      </c>
-      <c r="D47" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>10010008</v>
-      </c>
-      <c r="H47" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I47" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J47" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L47" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M47" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="N47" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O47" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P47" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q47" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R47" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S47" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T47" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U47" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V47" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W47" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X47" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y47" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z47" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA47" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB47" s="23" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" s="23">
-      <c r="A48" s="21" t="n">
-        <v>1065611</v>
-      </c>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>哮天犬</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="n">
-        <v>1052</v>
-      </c>
-      <c r="H48" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I48" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="J48" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K48" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L48" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M48" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="N48" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O48" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P48" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q48" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R48" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S48" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T48" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U48" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V48" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W48" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X48" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y48" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z48" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA48" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB48" s="23" t="n">
-        <v>100</v>
-      </c>
+      <c r="M48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n">
+        <v>90000013</v>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>试炼小妖</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>101,102</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="23" t="n"/>
+      <c r="K49" s="23" t="n"/>
+      <c r="L49" s="23" t="n"/>
+      <c r="M49" s="23" t="n"/>
+      <c r="N49" s="23" t="n"/>
+      <c r="O49" s="23" t="n"/>
+      <c r="P49" s="23" t="n"/>
+      <c r="Q49" s="23" t="n"/>
+      <c r="R49" s="23" t="n"/>
+      <c r="S49" s="23" t="n"/>
+      <c r="T49" s="23" t="n"/>
+      <c r="U49" s="23" t="n"/>
+      <c r="V49" s="23" t="n"/>
+      <c r="W49" s="23" t="n"/>
+      <c r="X49" s="23" t="n"/>
+      <c r="Y49" s="23" t="n"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="23" t="n"/>
+      <c r="AB49" s="23" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">

--- a/resources/combat/pve_combat_npc.xlsx
+++ b/resources/combat/pve_combat_npc.xlsx
@@ -398,7 +398,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -468,15 +468,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1315,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1718,7 +1709,7 @@
         <v>1012</v>
       </c>
       <c r="D5" s="17" t="n"/>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1806,7 +1797,7 @@
         <v>1012</v>
       </c>
       <c r="D6" s="17" t="n"/>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1895,7 +1886,7 @@
         <v>1057</v>
       </c>
       <c r="D7" s="17" t="n"/>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -1983,7 +1974,7 @@
         <v>1060</v>
       </c>
       <c r="D8" s="17" t="n"/>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2071,7 +2062,7 @@
         <v>1062</v>
       </c>
       <c r="D9" s="17" t="n"/>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2159,7 +2150,7 @@
         <v>1012</v>
       </c>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>1001,1002,1003</t>
         </is>
@@ -2257,7 +2248,7 @@
       <c r="A12" s="18" t="n">
         <v>8032</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>分身</t>
         </is>
@@ -2296,7 +2287,7 @@
       <c r="I13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J13" s="16" t="n">
         <v>2000</v>
       </c>
       <c r="K13" s="13" t="n">
@@ -3434,1720 +3425,1665 @@
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="8">
-      <c r="A28" s="21" t="n">
-        <v>1065601</v>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>杨戬</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>1065</v>
-      </c>
-      <c r="D28" s="23" t="n">
+      <c r="A28" s="18" t="n">
+        <v>90000001</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩1</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D28" s="17" t="n"/>
+      <c r="H28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="23" t="n">
-        <v>10010001</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="J28" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M28" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N28" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q28" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V28" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="W28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA28" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB28" s="23" t="n">
-        <v>100</v>
+      <c r="I28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13" t="n">
+        <v>1657</v>
+      </c>
+      <c r="S28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC28" s="0" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="8">
-      <c r="A29" s="21" t="n">
-        <v>1065602</v>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>李靖</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D29" s="23" t="n">
+      <c r="A29" s="18" t="n">
+        <v>90000002</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩2</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D29" s="17" t="n"/>
+      <c r="H29" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="23" t="n">
-        <v>10010002</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I29" s="23" t="n">
-        <v>450</v>
-      </c>
-      <c r="J29" s="23" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M29" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="N29" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O29" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="P29" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q29" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="R29" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S29" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="T29" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U29" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V29" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z29" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA29" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB29" s="23" t="n">
-        <v>100</v>
+      <c r="I29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13" t="n">
+        <v>2932</v>
+      </c>
+      <c r="S29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC29" s="0" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="8">
-      <c r="A30" s="21" t="n">
-        <v>1065603</v>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>哪吒</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D30" s="23" t="n">
+      <c r="A30" s="18" t="n">
+        <v>90000003</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩3</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D30" s="17" t="n"/>
+      <c r="H30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="23" t="n">
-        <v>10010003</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J30" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O30" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P30" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q30" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S30" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U30" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="W30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z30" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA30" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB30" s="23" t="n">
-        <v>100</v>
+      <c r="I30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>3187</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="13" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="W30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Y30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="13" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AA30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="13" t="n">
+        <v>1275</v>
       </c>
       <c r="AC30" s="0" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="8">
-      <c r="A31" s="21" t="n">
-        <v>1065604</v>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>梅山·康太尉</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="n">
-        <v>1058</v>
-      </c>
-      <c r="D31" s="23" t="n">
+      <c r="A31" s="18" t="n">
+        <v>90000004</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩4</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D31" s="17" t="n"/>
+      <c r="H31" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="23" t="n">
-        <v>10010004</v>
-      </c>
-      <c r="H31" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I31" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J31" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L31" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N31" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P31" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q31" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R31" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T31" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="W31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA31" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB31" s="23" t="n">
-        <v>100</v>
+      <c r="I31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="AC31" s="0" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="8">
-      <c r="A32" s="21" t="n">
-        <v>1065605</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>梅山·张太尉</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D32" s="23" t="n">
+      <c r="A32" s="18" t="n">
+        <v>90000005</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩5</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D32" s="17" t="n"/>
+      <c r="H32" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="23" t="n">
-        <v>10010005</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I32" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J32" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L32" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N32" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P32" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q32" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T32" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U32" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="V32" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA32" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB32" s="23" t="n">
-        <v>100</v>
+      <c r="I32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="AC32" s="0" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="8">
-      <c r="A33" s="21" t="n">
-        <v>1065606</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>梅山·李太尉</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D33" s="23" t="n">
+      <c r="A33" s="18" t="n">
+        <v>90000006</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩6</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D33" s="17" t="n"/>
+      <c r="H33" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G33" s="23" t="n">
-        <v>10010006</v>
-      </c>
-      <c r="H33" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J33" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L33" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M33" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="N33" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O33" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q33" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S33" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T33" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U33" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z33" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA33" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB33" s="23" t="n">
-        <v>100</v>
+      <c r="I33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="8">
-      <c r="A34" s="21" t="n">
-        <v>1065607</v>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>梅山·姚太尉</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D34" s="23" t="n">
+      <c r="A34" s="18" t="n">
+        <v>90000007</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩7</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D34" s="17" t="n"/>
+      <c r="H34" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G34" s="23" t="n">
-        <v>10010007</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="J34" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L34" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="N34" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O34" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P34" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q34" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="R34" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S34" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="T34" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V34" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB34" s="23" t="n">
-        <v>100</v>
+      <c r="I34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="8">
-      <c r="A35" s="21" t="n">
-        <v>1065609</v>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>巨灵神</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="A35" s="18" t="n">
+        <v>90000008</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩8</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
         <v>1059</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="17" t="n"/>
+      <c r="H35" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G35" s="23" t="n">
-        <v>10010008</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="J35" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L35" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M35" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="N35" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O35" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P35" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q35" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R35" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S35" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U35" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V35" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="W35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB35" s="23" t="n">
-        <v>100</v>
+      <c r="I35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="8">
-      <c r="A36" s="21" t="n">
-        <v>1065611</v>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>哮天犬</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>1052</v>
+      <c r="A36" s="18" t="n">
+        <v>90000009</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>测试木桩9</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>1060</v>
       </c>
       <c r="D36" s="17" t="n"/>
-      <c r="H36" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>150</v>
-      </c>
-      <c r="J36" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L36" s="23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M36" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="N36" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="O36" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q36" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R36" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="S36" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" s="23" t="n">
-        <v>550</v>
-      </c>
-      <c r="U36" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V36" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="W36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z36" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA36" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB36" s="23" t="n">
-        <v>100</v>
+      <c r="H36" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="8">
       <c r="A37" s="18" t="n">
-        <v>90000001</v>
+        <v>90000010</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>测试木桩1</t>
+          <t>测试木桩10</t>
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="D37" s="17" t="n"/>
       <c r="H37" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>10</v>
+        <v>100000000</v>
       </c>
       <c r="K37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>10</v>
+        <v>100000000</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="13" t="n">
-        <v>1657</v>
+        <v>0</v>
       </c>
       <c r="S37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB37" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC37" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="8">
       <c r="A38" s="18" t="n">
-        <v>90000002</v>
+        <v>90000011</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>测试木桩2</t>
+          <t>测试木桩11</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>1053</v>
+        <v>1062</v>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="H38" s="11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>100</v>
+        <v>500000000</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>100</v>
+        <v>500000000</v>
       </c>
       <c r="M38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>2932</v>
+        <v>0</v>
       </c>
       <c r="S38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z38" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB38" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC38" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="8">
       <c r="A39" s="18" t="n">
-        <v>90000003</v>
+        <v>90000012</v>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>测试木桩3</t>
+          <t>测试木桩12</t>
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="D39" s="17" t="n"/>
-      <c r="H39" s="11" t="n">
-        <v>3</v>
+      <c r="H39" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="K39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="13" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="S39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="W39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="13" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AB39" s="13" t="n">
-        <v>1275</v>
-      </c>
-      <c r="AC39" s="0" t="n"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="1" s="23">
-      <c r="A40" s="18" t="n">
-        <v>90000004</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩4</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D40" s="17" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="0" t="n"/>
+      <c r="A40" s="21" t="n">
+        <v>1065601</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>杨戬</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>10010001</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="J40" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L40" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M40" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N40" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P40" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q40" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V40" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="W40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA40" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB40" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41" customFormat="1" s="23">
-      <c r="A41" s="18" t="n">
-        <v>90000005</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩5</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D41" s="17" t="n"/>
-      <c r="G41" s="23" t="n"/>
-      <c r="H41" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="13" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="0" t="n"/>
+      <c r="A41" s="21" t="n">
+        <v>1065602</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>李靖</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>10010002</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="J41" s="23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L41" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M41" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="N41" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O41" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P41" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q41" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S41" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T41" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U41" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V41" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z41" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB41" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="42" customFormat="1" s="23">
-      <c r="A42" s="18" t="n">
-        <v>90000006</v>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩6</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="13" t="n">
-        <v>0</v>
+      <c r="A42" s="21" t="n">
+        <v>1065603</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>哪吒</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>10010003</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J42" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O42" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P42" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q42" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="R42" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S42" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="W42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA42" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB42" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="43" customFormat="1" s="23">
-      <c r="A43" s="18" t="n">
-        <v>90000007</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩7</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="n">
+      <c r="A43" s="21" t="n">
+        <v>1065604</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>梅山·康太尉</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
         <v>1058</v>
       </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="M43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="13" t="n">
-        <v>0</v>
+      <c r="D43" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>10010004</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J43" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L43" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q43" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U43" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="V43" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="W43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA43" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB43" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="1" s="23">
-      <c r="A44" s="18" t="n">
-        <v>90000008</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩8</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>1059</v>
-      </c>
-      <c r="D44" s="17" t="n"/>
-      <c r="G44" s="23" t="n"/>
-      <c r="H44" s="11" t="n">
+      <c r="A44" s="21" t="n">
+        <v>1065605</v>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>梅山·张太尉</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>10010005</v>
+      </c>
+      <c r="H44" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L44" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O44" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="13" t="n">
-        <v>0</v>
+      <c r="P44" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S44" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U44" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="V44" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB44" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="45" customFormat="1" s="23">
-      <c r="A45" s="18" t="n">
-        <v>90000009</v>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩9</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>1060</v>
-      </c>
-      <c r="D45" s="17" t="n"/>
-      <c r="G45" s="23" t="n"/>
-      <c r="H45" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="13" t="n">
-        <v>0</v>
+      <c r="A45" s="21" t="n">
+        <v>1065606</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>梅山·李太尉</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>10010006</v>
+      </c>
+      <c r="H45" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J45" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M45" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N45" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O45" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S45" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U45" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V45" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB45" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="46" customFormat="1" s="23">
-      <c r="A46" s="18" t="n">
-        <v>90000010</v>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩10</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>1061</v>
-      </c>
-      <c r="D46" s="17" t="n"/>
-      <c r="G46" s="23" t="n"/>
-      <c r="H46" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="13" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="13" t="n">
-        <v>0</v>
+      <c r="A46" s="21" t="n">
+        <v>1065607</v>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>梅山·姚太尉</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>10010007</v>
+      </c>
+      <c r="H46" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="J46" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L46" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O46" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P46" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q46" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="R46" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S46" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z46" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB46" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="1" s="23">
-      <c r="A47" s="18" t="n">
-        <v>90000011</v>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩11</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>1062</v>
-      </c>
-      <c r="D47" s="17" t="n"/>
-      <c r="G47" s="23" t="n"/>
-      <c r="H47" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="K47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="13" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="M47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="13" t="n">
-        <v>0</v>
+      <c r="A47" s="21" t="n">
+        <v>1065609</v>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>巨灵神</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>10010008</v>
+      </c>
+      <c r="H47" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I47" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="J47" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M47" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="N47" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O47" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U47" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V47" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="W47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA47" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB47" s="23" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="1" s="23">
-      <c r="A48" s="18" t="n">
-        <v>90000012</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>测试木桩12</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>1063</v>
-      </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="H48" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="13" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="M48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="n">
-        <v>90000013</v>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
-        <is>
-          <t>试炼小妖</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>101,102</t>
-        </is>
-      </c>
-      <c r="H49" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="23" t="n"/>
-      <c r="J49" s="23" t="n"/>
-      <c r="K49" s="23" t="n"/>
-      <c r="L49" s="23" t="n"/>
-      <c r="M49" s="23" t="n"/>
-      <c r="N49" s="23" t="n"/>
-      <c r="O49" s="23" t="n"/>
-      <c r="P49" s="23" t="n"/>
-      <c r="Q49" s="23" t="n"/>
-      <c r="R49" s="23" t="n"/>
-      <c r="S49" s="23" t="n"/>
-      <c r="T49" s="23" t="n"/>
-      <c r="U49" s="23" t="n"/>
-      <c r="V49" s="23" t="n"/>
-      <c r="W49" s="23" t="n"/>
-      <c r="X49" s="23" t="n"/>
-      <c r="Y49" s="23" t="n"/>
-      <c r="Z49" s="23" t="n"/>
-      <c r="AA49" s="23" t="n"/>
-      <c r="AB49" s="23" t="n"/>
+      <c r="A48" s="21" t="n">
+        <v>1065611</v>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>哮天犬</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H48" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="J48" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L48" s="23" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M48" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="N48" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="O48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q48" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" s="23" t="n">
+        <v>250</v>
+      </c>
+      <c r="S48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" s="23" t="n">
+        <v>550</v>
+      </c>
+      <c r="U48" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="V48" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="W48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB48" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A9">
